--- a/docs/Mapping_casi_uso/morte/Morte_019.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_019.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="204">
   <si>
     <t>Sezione</t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t>testoDataPresuntaMorte</t>
+  </si>
+  <si>
+    <t>Data rinvenimento cadavere</t>
+  </si>
+  <si>
+    <t>dataRinvenimentoCadavere</t>
   </si>
   <si>
     <t>Luogo</t>
@@ -676,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.12890625" customWidth="true" bestFit="true"/>
@@ -1219,19 +1225,19 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>10</v>
@@ -1242,16 +1248,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -1265,16 +1271,16 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -1288,7 +1294,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
@@ -1297,7 +1303,7 @@
         <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -1311,16 +1317,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -1334,16 +1340,16 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1357,7 +1363,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
@@ -1366,7 +1372,7 @@
         <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1380,16 +1386,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1403,7 +1409,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
@@ -1412,7 +1418,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
@@ -1426,7 +1432,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
@@ -1435,7 +1441,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1449,16 +1455,16 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1472,7 +1478,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>83</v>
@@ -1481,7 +1487,7 @@
         <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>84</v>
@@ -1495,7 +1501,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>85</v>
@@ -1504,7 +1510,7 @@
         <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>86</v>
@@ -1518,7 +1524,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
@@ -1527,7 +1533,7 @@
         <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>88</v>
@@ -1541,7 +1547,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>89</v>
@@ -1550,7 +1556,7 @@
         <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>90</v>
@@ -1564,16 +1570,16 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>92</v>
@@ -1587,7 +1593,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>93</v>
@@ -1596,7 +1602,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>94</v>
@@ -1610,16 +1616,16 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>96</v>
@@ -1633,7 +1639,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>97</v>
@@ -1642,7 +1648,7 @@
         <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>98</v>
@@ -1656,7 +1662,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>99</v>
@@ -1665,7 +1671,7 @@
         <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>100</v>
@@ -1679,7 +1685,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>101</v>
@@ -1688,7 +1694,7 @@
         <v>12</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>102</v>
@@ -1702,7 +1708,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>103</v>
@@ -1711,7 +1717,7 @@
         <v>12</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>104</v>
@@ -1725,7 +1731,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>105</v>
@@ -1734,7 +1740,7 @@
         <v>12</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>106</v>
@@ -1748,7 +1754,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>107</v>
@@ -1757,7 +1763,7 @@
         <v>12</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>108</v>
@@ -1771,7 +1777,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>109</v>
@@ -1780,7 +1786,7 @@
         <v>12</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>110</v>
@@ -1794,7 +1800,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>111</v>
@@ -1803,7 +1809,7 @@
         <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>112</v>
@@ -1817,7 +1823,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>113</v>
@@ -1826,7 +1832,7 @@
         <v>12</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>114</v>
@@ -1840,7 +1846,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>115</v>
@@ -1849,7 +1855,7 @@
         <v>12</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>116</v>
@@ -1863,7 +1869,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>117</v>
@@ -1872,7 +1878,7 @@
         <v>12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>118</v>
@@ -1886,39 +1892,39 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="C53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>121</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>64</v>
@@ -1927,35 +1933,35 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>69</v>
@@ -1964,7 +1970,7 @@
         <v>12</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>70</v>
@@ -1973,12 +1979,12 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>71</v>
@@ -1987,7 +1993,7 @@
         <v>12</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>72</v>
@@ -1996,12 +2002,12 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>73</v>
@@ -2010,7 +2016,7 @@
         <v>12</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>74</v>
@@ -2019,12 +2025,12 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>75</v>
@@ -2033,7 +2039,7 @@
         <v>12</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>76</v>
@@ -2042,21 +2048,21 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>78</v>
@@ -2065,21 +2071,21 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>80</v>
@@ -2088,21 +2094,21 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>82</v>
@@ -2111,21 +2117,21 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>84</v>
@@ -2134,21 +2140,21 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>86</v>
@@ -2157,21 +2163,21 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>88</v>
@@ -2180,21 +2186,21 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>90</v>
@@ -2203,12 +2209,12 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>91</v>
@@ -2217,7 +2223,7 @@
         <v>12</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>92</v>
@@ -2226,21 +2232,21 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>94</v>
@@ -2249,67 +2255,67 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>98</v>
@@ -2318,21 +2324,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>100</v>
@@ -2341,21 +2347,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>102</v>
@@ -2364,21 +2370,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>104</v>
@@ -2387,21 +2393,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>106</v>
@@ -2410,21 +2416,21 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>108</v>
@@ -2433,21 +2439,21 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>110</v>
@@ -2456,35 +2462,35 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>140</v>
@@ -2493,7 +2499,7 @@
         <v>12</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>141</v>
@@ -2502,12 +2508,12 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>142</v>
@@ -2516,7 +2522,7 @@
         <v>12</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>143</v>
@@ -2525,44 +2531,44 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="C81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>64</v>
@@ -2571,35 +2577,35 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>69</v>
@@ -2608,7 +2614,7 @@
         <v>12</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>70</v>
@@ -2617,12 +2623,12 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>71</v>
@@ -2631,7 +2637,7 @@
         <v>12</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>72</v>
@@ -2640,12 +2646,12 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>73</v>
@@ -2654,7 +2660,7 @@
         <v>12</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>74</v>
@@ -2663,12 +2669,12 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>75</v>
@@ -2677,7 +2683,7 @@
         <v>12</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>76</v>
@@ -2686,21 +2692,21 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>78</v>
@@ -2709,21 +2715,21 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>80</v>
@@ -2732,21 +2738,21 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>82</v>
@@ -2755,21 +2761,21 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>84</v>
@@ -2778,21 +2784,21 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>86</v>
@@ -2801,21 +2807,21 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>88</v>
@@ -2824,21 +2830,21 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>90</v>
@@ -2847,12 +2853,12 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>91</v>
@@ -2861,7 +2867,7 @@
         <v>12</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>92</v>
@@ -2870,21 +2876,21 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>94</v>
@@ -2893,67 +2899,67 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>98</v>
@@ -2962,21 +2968,21 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>100</v>
@@ -2985,21 +2991,21 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>102</v>
@@ -3008,21 +3014,21 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>104</v>
@@ -3031,21 +3037,21 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>106</v>
@@ -3054,21 +3060,21 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>108</v>
@@ -3077,21 +3083,21 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>110</v>
@@ -3100,35 +3106,35 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>140</v>
@@ -3137,7 +3143,7 @@
         <v>12</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>141</v>
@@ -3146,12 +3152,12 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>142</v>
@@ -3160,7 +3166,7 @@
         <v>12</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>143</v>
@@ -3169,7 +3175,7 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="109">
@@ -3177,36 +3183,36 @@
         <v>146</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G109" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>151</v>
@@ -3220,7 +3226,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>152</v>
@@ -3229,7 +3235,7 @@
         <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>153</v>
@@ -3243,16 +3249,16 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>155</v>
@@ -3266,7 +3272,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>156</v>
@@ -3275,7 +3281,7 @@
         <v>12</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>157</v>
@@ -3289,7 +3295,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>158</v>
@@ -3298,7 +3304,7 @@
         <v>12</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>159</v>
@@ -3312,7 +3318,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>160</v>
@@ -3321,7 +3327,7 @@
         <v>12</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>161</v>
@@ -3335,19 +3341,19 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C116" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3358,7 +3364,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>165</v>
@@ -3367,7 +3373,7 @@
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>166</v>
@@ -3381,53 +3387,53 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="C118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>171</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B119" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E119" s="2" t="s">
+      <c r="F119" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G119" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G119" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>174</v>
@@ -3436,7 +3442,7 @@
         <v>12</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>175</v>
@@ -3445,12 +3451,12 @@
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>176</v>
@@ -3459,7 +3465,7 @@
         <v>12</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>177</v>
@@ -3468,12 +3474,12 @@
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>178</v>
@@ -3482,7 +3488,7 @@
         <v>12</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>179</v>
@@ -3491,12 +3497,12 @@
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>180</v>
@@ -3505,7 +3511,7 @@
         <v>12</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>181</v>
@@ -3514,12 +3520,12 @@
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>182</v>
@@ -3528,44 +3534,44 @@
         <v>12</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>184</v>
+        <v>17</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>185</v>
@@ -3574,44 +3580,44 @@
         <v>12</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>188</v>
@@ -3620,7 +3626,7 @@
         <v>12</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>189</v>
@@ -3629,12 +3635,12 @@
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>190</v>
@@ -3643,7 +3649,7 @@
         <v>12</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>191</v>
@@ -3652,12 +3658,12 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>192</v>
@@ -3666,7 +3672,7 @@
         <v>12</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>193</v>
@@ -3675,44 +3681,44 @@
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="C131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B132" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>199</v>
@@ -3726,7 +3732,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>200</v>
@@ -3735,7 +3741,7 @@
         <v>12</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>201</v>
@@ -3744,6 +3750,29 @@
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G134" s="2" t="s">
         <v>18</v>
       </c>
     </row>
